--- a/data/google_news_dedup_30_0326_UTC_past2d.xlsx
+++ b/data/google_news_dedup_30_0326_UTC_past2d.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -655,22 +655,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DHL expands South African supply chain with key acquisitions - Business Day</t>
+          <t>FedEx announces major change to delivery times - MSN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DHL expands South African supply chain with key acquisitions - Business Day</t>
+          <t>FedEx announces major change to delivery times - MSN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 03:00:00 GMT</t>
+          <t>Mon, 30 Mar 2026 03:36:54 GMT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNM2tlNmFPcW1lTGhnUVpHVmZvUDBuTkFRVmVvQVZKSkQ4RGc5VjJsVzd1SVNvbkQwR0JCa0dqOTJmODdUb3RLdFB1QmxBS05DaWxTSXFXLVpVTzZ1YTR3WXViSjNVM2F5d0g1WXZlV1NXQmFMVnFDQ01VVzRXV3dQOWpYbEdpNF9mclZVd0JjY09OdE5GNWZhd041b1BYVDJMMDJSeTdZMEdERmtFSFFIUU53?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPVl9lNXVHampQTlE1WnhSa1U1emFTakR2VjVrLW50eGFEdF9MOGE1a05UT3pGNDhPRXZPSjRReXl3QnBqMG5BU2xGdEd1SmI4aUNibFB1Y0JvZ3ZHSkVEdEZkWURtczlNNFE4dkVseTY4WWxOSC1QZ2VScHNzdTVZZEhmMFBnSnkySFk4Z2k1WGliRWU1NkpCRTB3eTVOdks0ZjVIRkpNVDZlMEpuTHpYQXpzelpVUF80b1R2RHJsS1ZXRW4w?oc=5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="K5" s="1" t="n">
-        <v>46111.125</v>
+        <v>46111.150625</v>
       </c>
     </row>
     <row r="6">
@@ -710,22 +710,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kroger inks Ocado grocery delivery deal to battle Amazon threat - AOL.com</t>
+          <t>DHL expands South African supply chain with key acquisitions - Business Day</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kroger inks Ocado grocery delivery deal to battle Amazon threat - AOL.com</t>
+          <t>DHL expands South African supply chain with key acquisitions - Business Day</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 00:17:32 GMT</t>
+          <t>Mon, 30 Mar 2026 03:00:00 GMT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQelhILU5INzRidUsyanMzNUNicnRxV1R3dlkwQVlLS1A5aENiVjN1Q3VuWDZ0SEpXZ2NuRlpmdWdFSlVFQTVUWWlqTGp5SFdlMDAwRzBDenBMV184ZThpd0c5dnp2V2hCSVlqcDJWam9PWDdjbXFvM091Sk1LV3E3ZURPamlla2NnUzU3c2tB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNM2tlNmFPcW1lTGhnUVpHVmZvUDBuTkFRVmVvQVZKSkQ4RGc5VjJsVzd1SVNvbkQwR0JCa0dqOTJmODdUb3RLdFB1QmxBS05DaWxTSXFXLVpVTzZ1YTR3WXViSjNVM2F5d0g1WXZlV1NXQmFMVnFDQ01VVzRXV3dQOWpYbEdpNF9mclZVd0JjY09OdE5GNWZhd041b1BYVDJMMDJSeTdZMEdERmtFSFFIUU53?oc=5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="K6" s="1" t="n">
-        <v>46111.01217592593</v>
+        <v>46111.125</v>
       </c>
     </row>
     <row r="7">
@@ -765,22 +765,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FedEx announces major change to delivery times - MSN</t>
+          <t>Amazon and USPS Negotiations Are Crumbling. Will This Hurt the eCommerce Giant's Stock? - AOL.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FedEx announces major change to delivery times - MSN</t>
+          <t>Amazon and USPS Negotiations Are Crumbling. Will This Hurt the eCommerce Giant's Stock? - AOL.com</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 03:36:54 GMT</t>
+          <t>Mon, 30 Mar 2026 05:51:27 GMT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPVl9lNXVHampQTlE1WnhSa1U1emFTakR2VjVrLW50eGFEdF9MOGE1a05UT3pGNDhPRXZPSjRReXl3QnBqMG5BU2xGdEd1SmI4aUNibFB1Y0JvZ3ZHSkVEdEZkWURtczlNNFE4dkVseTY4WWxOSC1QZ2VScHNzdTVZZEhmMFBnSnkySFk4Z2k1WGliRWU1NkpCRTB3eTVOdks0ZjVIRkpNVDZlMEpuTHpYQXpzelpVUF80b1R2RHJsS1ZXRW4w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5OanpCcktUMzh5cDYtVkl1cVRNTDlYWE9ZWlFNMVBxUmYxeE5FVk1TS1Vpelk4cWdSN0pKeTFiWWVJd01GZnBvbF96NExuUzhFdE9yOHF0YVgydmt6amxQVTlyVUFWU00yRmJRVUNEU1dkRnMxU190b0d3ejdwUHM?oc=5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46111.150625</v>
+        <v>46111.2440625</v>
       </c>
     </row>
     <row r="8">
@@ -820,22 +820,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amazon and USPS Negotiations Are Crumbling. Will This Hurt the eCommerce Giant's Stock? - AOL.com</t>
+          <t>TFG partners with DHL Supply Chain to open a temperature-controlled distribution center to support its retail business expansion plans. - moneyandbanking.co.th</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Amazon and USPS Negotiations Are Crumbling. Will This Hurt the eCommerce Giant's Stock? - AOL.com</t>
+          <t>TFG partners with DHL Supply Chain to open a temperature-controlled distribution center to support its retail business expansion plans. - moneyandbanking.co.th</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 04:46:41 GMT</t>
+          <t>Mon, 30 Mar 2026 04:37:34 GMT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5OanpCcktUMzh5cDYtVkl1cVRNTDlYWE9ZWlFNMVBxUmYxeE5FVk1TS1Vpelk4cWdSN0pKeTFiWWVJd01GZnBvbF96NExuUzhFdE9yOHF0YVgydmt6amxQVTlyVUFWU00yRmJRVUNEU1dkRnMxU190b0d3ejdwUHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5DYmgtUW1SVWlFQmVoMTVvdFRPenBzU055SW91dlNPVHdEXzY0d3VFcnRaSFp1VDRpY2MxWXVIczREc040Z0FXSjZwbkVHci1rT3U0M21QYjA?oc=5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="K8" s="1" t="n">
-        <v>46111.19908564815</v>
+        <v>46111.19275462963</v>
       </c>
     </row>
     <row r="9">
@@ -875,17 +875,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Voortvluchtige verdachte van dodelijke schietpartij op Belgische agent in Australië door politie doodgeschoten - nieuwsblad.be</t>
+          <t>Australische politie traceert verdachte die Belgische agent zou hebben gedood en schiet hem neer - Nieuwsblad</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fugitive suspect in fatal shooting of Belgian officer in Australia shot dead by police -nieuwsblad.be</t>
+          <t>Australian police track down suspect who allegedly killed Belgian police officer and shoot him - Nieuwsblad</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 05:54:09 GMT</t>
+          <t>Mon, 30 Mar 2026 07:24:09 GMT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="K9" s="1" t="n">
-        <v>46111.2459375</v>
+        <v>46111.3084375</v>
       </c>
     </row>
     <row r="10">
@@ -930,22 +930,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Neos Kuringen gaat een dagje op verkenning in Brussel - nieuwsblad.be</t>
+          <t>Blauwhelm gedood bij aanval in zuiden van Libanon - Nieuwsblad</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Neos Kuringen goes on a day of exploration in Brussels - nieuwsblad.be</t>
+          <t>Blue helmet killed in attack in south of Lebanon - Nieuwsblad</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 04:32:47 GMT</t>
+          <t>Mon, 30 Mar 2026 05:47:09 GMT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNNjUyMUZ2SmZ5SmttTEpaZTZad1I2VkpvdzFJY3J0eEVMeFNfckNZM0otQzd3QkwyOXJ1YTlqVXU1U3d0UlhTZWdmUlQ5VEc3SlVoZzFSaG1vc0N6OWw3bTBoOFJ0YVZDaE9XdElBSkxSZkU2U2dMQVllQ3doSG56YzRvODl0NGtUckdvaGFvSEcyZUszbERWSjVHWURneG5VUEtOeGw5Tnl2SDNRYTI0ekVzLUp1WkU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPa3hMZFNoMWIwUkoxTjVWa3FxT2hPaGY0X3gxV2NsR25pTjRjRmhrUnBmVVpEdEhCeElkR0R6RWRPZ0ZiUmNhVE5FeHh2SDZBOHN5Y1BmV3pBZUxaMlV2TExKaHlYWUlKd3pJZG5oWTlmbnRuNFFZNUNlcU1mWE43NWZaMFNFT3FjelpsdHJxMU5jYWFVWkR2Nzhsd2pBSGdOZzRr?oc=5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="K10" s="1" t="n">
-        <v>46111.18943287037</v>
+        <v>46111.24107638889</v>
       </c>
     </row>
     <row r="11">
@@ -985,22 +985,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vandalen vernielen portretten van slachtoffers aanslagen in Brussel: “We zijn in shock” - HBVL</t>
+          <t>Auto ramt tegen twee geparkeerde auto’s in Venlo - De Limburger</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Vandals destroy portraits of victims of attacks in Brussels: “We are in shock” - HBVL</t>
+          <t>Car rams into two parked cars in Venlo - De Limburger</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 00:41:00 GMT</t>
+          <t>Mon, 30 Mar 2026 04:26:35 GMT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNQ0NwbWR5TW8xck9RNHJURGNpRlVuN205RHREa0pDV0FnLW9PRndjaElDUTAxbHdoaWdvanlXTy1tZ083LVBPaHJLUVVUZ3Y0MXprWmJNdW5KVlAzc0lpZ2lucUthLTFndjkxOHVwMEU2MjVKc25vblpIY0h2QmxlYTN5QTlidS1WclJjM29tMDR1a0d0OXpOUk5Rc0pGWlpfMTJVeDV2RXBPMnRMOUFTcVZaTHhZN0NGYzZKSVpBT2VtRFYwcGFvb1FR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOanpGTEdwcWNHTjRlU0x0bnd1T2dnUDNvbE11eHZpYkdYS0tRdFY3RlJtRDdYOWdHUWprZDFyV3Y2TnY2SktmdGtEbzVwZXFEQU9rQlRKQWw1andtcXFpdEloTmJLd3ZQS2VIOEdidW83aDJTRU1saE9YQ1VlYlhMTW5EM1RKTk4zUTlMWXNuUlRSQldJcTdqWlJyS1JpNV8zN0p1X2dZTkE?oc=5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1024,38 +1024,38 @@
         </is>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46111.02847222222</v>
+        <v>46111.18512731481</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>High Level City Belgium English</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Auto ramt tegen twee geparkeerde auto’s in Venlo - De Limburger</t>
+          <t>Watch 9News Latest Stories - Season 2026 - Savannah Guthrie's first interview since the disappearance of her mother - 9Now</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Car rams into two parked cars in Venlo - De Limburger</t>
+          <t>Watch 9News Latest Stories - Season 2026 - Savannah Guthrie's first interview since the disappearance of her mother - 9Now</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 04:26:35 GMT</t>
+          <t>Mon, 30 Mar 2026 01:59:51 GMT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOanpGTEdwcWNHTjRlU0x0bnd1T2dnUDNvbE11eHZpYkdYS0tRdFY3RlJtRDdYOWdHUWprZDFyV3Y2TnY2SktmdGtEbzVwZXFEQU9rQlRKQWw1andtcXFpdEloTmJLd3ZQS2VIOEdidW83aDJTRU1saE9YQ1VlYlhMTW5EM1RKTk4zUTlMWXNuUlRSQldJcTdqWlJyS1JpNV8zN0p1X2dZTkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNV3RTc25YbGd0WXJYV29WOHpiNTZwckJwQi1OM0oySXNFZUFMMzdwQXFXX2hzUWZqSGdfNTBUb1JoV0Y1N19tQkVKaTNjS0dsdFdWbWZMSkxxWjE0bWxnTlRNT1NOTExzMm11RFpuakJ5eXQtdURkTl9NckJUS1ZQellBTDVTUkpJNWc2eA?oc=5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1075,11 +1075,11 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46111.18512731481</v>
+        <v>46111.08322916667</v>
       </c>
     </row>
     <row r="13">
@@ -1095,22 +1095,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Watch 9News Latest Stories - Season 2026 - Savannah Guthrie's first interview since the disappearance of her mother - 9Now</t>
+          <t>Watch 9News Latest Stories - Season 2026 - Tributes flow for beloved TV personality Mel Schilling - 9Now</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Watch 9News Latest Stories - Season 2026 - Savannah Guthrie's first interview since the disappearance of her mother - 9Now</t>
+          <t>Watch 9News Latest Stories - Season 2026 - Tributes flow for beloved TV personality Mel Schilling - 9Now</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 01:59:51 GMT</t>
+          <t>Mon, 30 Mar 2026 04:17:56 GMT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNV3RTc25YbGd0WXJYV29WOHpiNTZwckJwQi1OM0oySXNFZUFMMzdwQXFXX2hzUWZqSGdfNTBUb1JoV0Y1N19tQkVKaTNjS0dsdFdWbWZMSkxxWjE0bWxnTlRNT1NOTExzMm11RFpuakJ5eXQtdURkTl9NckJUS1ZQellBTDVTUkpJNWc2eA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOTWVFVVpTU1BxVXlTV0VrNHJzdVpuUEFISkpGaEs5RzlwZGR0LUJzQ2V0MWxuc2xpd1UtOVRJbERGWXYtblVxNGFKVEVWdnF3N29sazJhd00xWXgwWk5iVy1sSGpTNE92aHk5di1vOVNIMlBKU1VmZWE2cDBnSUdMTE5qVkxBV1BNN3c2Tw?oc=5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1134,38 +1134,38 @@
         </is>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46111.08322916667</v>
+        <v>46111.17912037037</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>High Level City Belgium English</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Watch 9News Latest Stories - Season 2026 - Tributes flow for beloved TV personality Mel Schilling - 9Now</t>
+          <t>Konjufca : L'attentat de Banjska, le dernier clou dans le cercueil du dialogue de Bruxelles - koha.net</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Watch 9News Latest Stories - Season 2026 - Tributes flow for beloved TV personality Mel Schilling - 9Now</t>
+          <t>Konjufca: The Banjska attack, the final nail in the coffin of the Brussels dialogue - koha.net</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 04:17:56 GMT</t>
+          <t>Mon, 30 Mar 2026 03:00:46 GMT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOTWVFVVpTU1BxVXlTV0VrNHJzdVpuUEFISkpGaEs5RzlwZGR0LUJzQ2V0MWxuc2xpd1UtOVRJbERGWXYtblVxNGFKVEVWdnF3N29sazJhd00xWXgwWk5iVy1sSGpTNE92aHk5di1vOVNIMlBKU1VmZWE2cDBnSUdMTE5qVkxBV1BNN3c2Tw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOd1NTR0RxaXFXRTVVX2dqZUsyek1SQWVrLUxRMU4zamtOMzVrZjRxNkZfZTk2WWkxNU90Nks2OWw5VURSS1AwLWx5cXFWTkxHY3JLYXNTWU9hYzZTYUFxVHRQZGJQZTBlS1BsRkREMENNLWxJMXZKcXBLY2tXY3dwVUc4ckVKTDU4Mk9wMlBhM2VVUzlra1UwYlJ6ZGUtV25GWTUxT0pJdHBsQQ?oc=5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1185,42 +1185,42 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>BE:en</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K14" s="1" t="n">
-        <v>46111.17912037037</v>
+        <v>46111.12553240741</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>Local Town Maasmechelen Dutch (fallback)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Konjufca : L'attentat de Banjska, le dernier clou dans le cercueil du dialogue de Bruxelles - koha.net</t>
+          <t>Gerechtskosten BNP actie Hasselt - Steunactie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Konjufca: The Banjska attack, the final nail in the coffin of the Brussels dialogue - koha.net</t>
+          <t>Legal costs BNP action Hasselt - Support action</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 03:00:46 GMT</t>
+          <t>Mon, 30 Mar 2026 02:49:20 GMT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOd1NTR0RxaXFXRTVVX2dqZUsyek1SQWVrLUxRMU4zamtOMzVrZjRxNkZfZTk2WWkxNU90Nks2OWw5VURSS1AwLWx5cXFWTkxHY3JLYXNTWU9hYzZTYUFxVHRQZGJQZTBlS1BsRkREMENNLWxJMXZKcXBLY2tXY3dwVUc4ckVKTDU4Mk9wMlBhM2VVUzlra1UwYlJ6ZGUtV25GWTUxT0pJdHBsQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5rWk1YcGNXNC1WNDhVRUtMaUM0TkZXUnRLUGV1QVJ1U01rZk5jLXM2ZzRKeHdfbE54M2xub1k3bnFKSE9hN0c2eFhxUGxpRUR5LVg5aF9wdmpoYThJSUh6SDZITkpRejZsNkxsMHVyYmdVVDZsUGZtZ2xB?oc=5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1240,42 +1240,42 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46111.12553240741</v>
+        <v>46111.11759259259</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>Local Town Maasmechelen Dutch (fallback)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Attentat déjoué contre Bank of America à Paris : deux nouvelles interpellations - lecourrier.vn</t>
+          <t>Talenten Academie Limburg stopt zaterdagschool in Beringen en zoekt nieuw concept - VRT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Foiled attack against Bank of America in Paris: two new arrests - lecourrier.vn</t>
+          <t>Talent Academy Limburg stops Saturday school in Beringen and looks for a new concept - VRT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 01:04:00 GMT</t>
+          <t>Mon, 30 Mar 2026 07:01:18 GMT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNNjBpSl9hdy1WMURGY1Vha0NZbEZLd3h5dXM5UlZnRURRQkZLRjNSV2NWalZVTk5rdjZmMVprUWlKSm1rX0haWm5kM3l0SFljaHo4bzZDY20ydUxOWXotNGpGU2hfMGxBNGpRc0MtaXlydkhaMEVoVG1rQTJuOW45bk9ZMkNWVC1wemxjWEhrYUNpVGlPZ0Q4MmNLU3UyQzRmcDFCZG5iUFNEM3RQQVdCdDl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPY2tSZWt3UXZaNUFxQlBsdVBhR2MtdEx4SEFfNUstMC1wNm9jMzNtaThmWjRzNGxWVDhHb2drai11TFJ2OHVqYThabHpsT1N6WEpHZXBLSWNheFVMWkVOMnF0ZVVQTENBN0Jpd3NhS2hyWjN4eXVOZ3hHWnMzQXA1MU1qTkVsblpjN0FHYU5Nc0xMVFp2Y2NJR2ROazBlMkU?oc=5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1295,11 +1295,11 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K16" s="1" t="n">
-        <v>46111.04444444444</v>
+        <v>46111.29256944444</v>
       </c>
     </row>
     <row r="17">
@@ -1315,22 +1315,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gerechtskosten BNP actie Hasselt - Steunactie</t>
+          <t>100-jarige Maria Vanhengel zweert bij leven zonder alcohol - HLN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Legal costs BNP action Hasselt - Support action</t>
+          <t>100-year-old Maria Vanhengel swears by living without alcohol - HLN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 02:49:20 GMT</t>
+          <t>Mon, 30 Mar 2026 07:30:34 GMT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5rWk1YcGNXNC1WNDhVRUtMaUM0TkZXUnRLUGV1QVJ1U01rZk5jLXM2ZzRKeHdfbE54M2xub1k3bnFKSE9hN0c2eFhxUGxpRUR5LVg5aF9wdmpoYThJSUh6SDZITkpRejZsNkxsMHVyYmdVVDZsUGZtZ2xB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOX2dQWnU5WnREaEg5VkxNdldWWnpGUEt5QjVfVkk3aHEzZG9UQVpGQnc3VGNDRkZoaVBjNTZGZW5SMFBPLTdfMGhqVWY3UWtWWldLOFJvd3RhMkhFMVdMWVJBZl9qeDV0R3NHQXZiajNyS2tvb3RiXzdIdVN2azZHd05vSkpEZHYyTEVrRV9zVnFVZGQ3N2FYYk9lWQ?oc=5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46111.11759259259</v>
+        <v>46111.31289351852</v>
       </c>
     </row>
     <row r="18">
@@ -1370,22 +1370,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Talenten Academie Limburg stopt zaterdagschool in Beringen en zoekt nieuw concept - vrt.be</t>
+          <t>FC Knokke nadert na ultieme goal van Aske Sampers weer tot op één punt van leider Sporting Hasselt: “We hebben de laatste strohalm gegrepen” - Nieuwsblad</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Talent Academy Limburg stops Saturday school in Beringen and looks for a new concept - vrt.be</t>
+          <t>After the ultimate goal by Aske Sampers, FC Knokke comes within one point of leader Sporting Hasselt: “We have grabbed the last straw” - Nieuwsblad</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 07:01:18 GMT</t>
+          <t>Mon, 30 Mar 2026 02:43:01 GMT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPY2tSZWt3UXZaNUFxQlBsdVBhR2MtdEx4SEFfNUstMC1wNm9jMzNtaThmWjRzNGxWVDhHb2drai11TFJ2OHVqYThabHpsT1N6WEpHZXBLSWNheFVMWkVOMnF0ZVVQTENBN0Jpd3NhS2hyWjN4eXVOZ3hHWnMzQXA1MU1qTkVsblpjN0FHYU5Nc0xMVFp2Y2NJR2ROazBlMkU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxQWUFPTW1YLW9Lb01PeC11VmhfSWhGVzE3U1JOOUNqN0ZmYVgyeFhZYjhiS0pBdnI4NFIzeWJoaXNNVVFSZGs1R2lnSFV6NXNZU3A5V1VVVEtYSGh2djNIY2RBTHNoMjNHNndaM2l1dm5UaFVBRFpnY2ZTY213TUZWdDJJUDdsMkRsNDlsc3hlUUcxYV9aeWJpa2ZtMlZqN0J5c1JJZ1RXRjZFbTkxbi1CV0ZxWVpYdmNGYU12dHhTd09HQ05IT1YzbDBseHFlWFNIeTgzSkI4U21WeE9ZSkE1VEc3ZXFhU1I0QkV1emJtcWV3cWZVTk52QzBCVi1VSE9zMkl4bUZhWVJTOVNqU09nY3lBbmJhOGlRaXZVSVBjSDM?oc=5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46111.29256944444</v>
+        <v>46111.11320601852</v>
       </c>
     </row>
     <row r="19">
@@ -1425,22 +1425,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Stroomstoring in Kerkveld in Lanaken opgelost - hln.be</t>
+          <t>Pasar Lanaken neemt een kijkje achter de schermen van Dovy Keukens - HBVL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Power outage in Kerkveld in Lanaken resolved - hln.be</t>
+          <t>Pasar Lanaken takes a look behind the scenes of Dovy Keukens - HBVL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 00:50:55 GMT</t>
+          <t>Mon, 30 Mar 2026 03:45:11 GMT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOMDhjSW5XbXlmLUh1TFFVcjFoWFZVdEd1LVUxZ3F4anZsNlhYQ1Q5Y0RuVGZ0UW5YUmJNT2NmcDlxM29wNUN6aUVzbk80VkdXQWxMREd5dDl1S2pKLV9zdXhkd0FJOWZPenRzZTV1Wi1jS1UwR2pvQWk4V2pPSi00RFdzYnpSNlpDWWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOWm15M21DUXhLSWFaaDVra2o3ekRDTmg1Q1hDLVZoc1dERkw0TzgwNGduSTRJRkcwR1l5bWdDR2FFTTdxT1o1SWFsWk1mcnhTV3UxVWNHQ3ZYdjJYQlJOUDQtTHY4eEIxcm5xVXJmLS1qNVBzbGRKZjFQRkJ1c2NodkZpeGd2UWw5N2J5MWFQUmFweFJfZG1SVFRnZVFRU2pieVFBZmFqVUotQUE0RVNhWVkya0ZHZw?oc=5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="K19" s="1" t="n">
-        <v>46111.0353587963</v>
+        <v>46111.15637731482</v>
       </c>
     </row>
     <row r="20">
@@ -1480,22 +1480,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FC Knokke nadert na ultieme goal van Aske Sampers weer tot op één punt van leider Sporting Hasselt: “We hebben de laatste strohalm gegrepen” - nieuwsblad.be</t>
+          <t>“Ik zit met moordgedachten en ik heb een mes bij”: student (21) gaat naar spoed voor hulp, maar belandt in cel - HLN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FC Knokke comes within one point of leader Sporting Hasselt after the ultimate goal by Aske Sampers: “We have grabbed the last straw” -nieuwsblad.be</t>
+          <t>“I have homicidal thoughts and I have a knife”: student (21) goes to the emergency room for help, but ends up in jail - HLN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 02:43:01 GMT</t>
+          <t>Mon, 30 Mar 2026 03:40:44 GMT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxQWUFPTW1YLW9Lb01PeC11VmhfSWhGVzE3U1JOOUNqN0ZmYVgyeFhZYjhiS0pBdnI4NFIzeWJoaXNNVVFSZGs1R2lnSFV6NXNZU3A5V1VVVEtYSGh2djNIY2RBTHNoMjNHNndaM2l1dm5UaFVBRFpnY2ZTY213TUZWdDJJUDdsMkRsNDlsc3hlUUcxYV9aeWJpa2ZtMlZqN0J5c1JJZ1RXRjZFbTkxbi1CV0ZxWVpYdmNGYU12dHhTd09HQ05IT1YzbDBseHFlWFNIeTgzSkI4U21WeE9ZSkE1VEc3ZXFhU1I0QkV1emJtcWV3cWZVTk52QzBCVi1VSE9zMkl4bUZhWVJTOVNqU09nY3lBbmJhOGlRaXZVSVBjSDM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQdDdXaUZJTzBsWUFBTEhoSGlKTlVtMDY4M2hObF9xemRtdVNldE02YURPVmlpcmRtWDNqZ1QtR3UwMEFxUTN3UkFXRFBsOEZhSUxhaVQ3S3NES2NvbjhSenVpX1hYa2FpZzZhaURDOVpyci1CVnlMVmVDeVNPcldFdVRoV1RKYXZ2SWlqd2VkNFNBejZMcUliNUhjMVpYb2dnbXJpaUh4bHFxVDJ5LXUyUEkxOExGV2pJS0Q5SjAtTEpHd0kzbUhqcDVwR3VjQjVpd1FFbG1KTVA?oc=5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="K20" s="1" t="n">
-        <v>46111.11320601852</v>
+        <v>46111.15328703704</v>
       </c>
     </row>
     <row r="21">
@@ -1535,22 +1535,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pasar Lanaken neemt een kijkje achter de schermen van Dovy Keukens - HBVL</t>
+          <t>Stroomstoring in Kerkveld in Lanaken opgelost | Foto - HLN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Pasar Lanaken takes a look behind the scenes of Dovy Keukens - HBVL</t>
+          <t>Power outage in Kerkveld in Lanaken resolved | Photo - HLN</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 03:45:11 GMT</t>
+          <t>Mon, 30 Mar 2026 03:23:38 GMT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOWm15M21DUXhLSWFaaDVra2o3ekRDTmg1Q1hDLVZoc1dERkw0TzgwNGduSTRJRkcwR1l5bWdDR2FFTTdxT1o1SWFsWk1mcnhTV3UxVWNHQ3ZYdjJYQlJOUDQtTHY4eEIxcm5xVXJmLS1qNVBzbGRKZjFQRkJ1c2NodkZpeGd2UWw5N2J5MWFQUmFweFJfZG1SVFRnZVFRU2pieVFBZmFqVUotQUE0RVNhWVkya0ZHZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNaW02bWFEMWZEeU1ac2pQdnpDWW5vVnhuSGRyeG1WeV9MSEJXSnl5SGpmV1JvVmtSQ3NfUjlOWVNuQnMwc1BPV1N5cmJqMkROOXZha0I0ajN0VjlYTGx4MVE0ZXA4UUJHYkJFTmVpV2NsOU1pZ1I1LTlkaG0zN1NQX18xSk9fZ2hXSElyNmVTb1BLMUcycVJj?oc=5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="K21" s="1" t="n">
-        <v>46111.15637731482</v>
+        <v>46111.14141203704</v>
       </c>
     </row>
     <row r="22">
@@ -1590,22 +1590,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>“Ik zit met moordgedachten en ik heb een mes bij”: student (21) gaat naar spoed voor hulp, maar belandt in cel - hln.be</t>
+          <t>Dit zijn de voetbaluitslagen uit Lanaken van het weekend van 28 en 29 maart | Foto - HLN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>“I have homicidal thoughts and I have a knife”: student (21) goes to the emergency room for help, but ends up in jail - hln.be</t>
+          <t>These are the football results from Lanaken for the weekend of March 28 and 29 | Photo - HLN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 03:40:44 GMT</t>
+          <t>Mon, 30 Mar 2026 01:25:49 GMT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQdDdXaUZJTzBsWUFBTEhoSGlKTlVtMDY4M2hObF9xemRtdVNldE02YURPVmlpcmRtWDNqZ1QtR3UwMEFxUTN3UkFXRFBsOEZhSUxhaVQ3S3NES2NvbjhSenVpX1hYa2FpZzZhaURDOVpyci1CVnlMVmVDeVNPcldFdVRoV1RKYXZ2SWlqd2VkNFNBejZMcUliNUhjMVpYb2dnbXJpaUh4bHFxVDJ5LXUyUEkxOExGV2pJS0Q5SjAtTEpHd0kzbUhqcDVwR3VjQjVpd1FFbG1KTVA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPamowazE3WlNGT0RTNmNxcEp1a2xuT2NNeEFVX0dYVXJUdkxJOV9rWllhUm5XdkJwM3I5c3hwQVhPaTZkYVZwSHBNZTBiSGp1LWFjS0QtaHNZNUFEYldGWWQzU2FUakY0MGhzaEw2alpHWlJCOTNVWHVuR3VYd1NrTWwtTEx2dW1TTjZleTBsYVVlQm5PT2JJcnlRTkt1YzdBT245dmxrc1ZMeHE5ZDJrQlI5MG1MZ0x6OWZBekJ5OA?oc=5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="K22" s="1" t="n">
-        <v>46111.15328703704</v>
+        <v>46111.0595949074</v>
       </c>
     </row>
     <row r="23">
@@ -1645,22 +1645,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dit zijn de voetbaluitslagen uit Lanaken van het weekend van 28 en 29 maart | Foto - hln.be</t>
+          <t>Simone Vrijdags, 98 jaar - HBVL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>These are the football results from Lanaken for the weekend of March 28 and 29 | Photo - hln.be</t>
+          <t>Simone Vrijdags, 98 years old - HBVL</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 01:25:49 GMT</t>
+          <t>Mon, 30 Mar 2026 04:10:08 GMT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPamowazE3WlNGT0RTNmNxcEp1a2xuT2NNeEFVX0dYVXJUdkxJOV9rWllhUm5XdkJwM3I5c3hwQVhPaTZkYVZwSHBNZTBiSGp1LWFjS0QtaHNZNUFEYldGWWQzU2FUakY0MGhzaEw2alpHWlJCOTNVWHVuR3VYd1NrTWwtTEx2dW1TTjZleTBsYVVlQm5PT2JJcnlRTkt1YzdBT245dmxrc1ZMeHE5ZDJrQlI5MG1MZ0x6OWZBekJ5OA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQdmJhSElnRndNcmFPU2I3RDgxbHpjS3BTZkVvQVRIQWx2T3U1NGJXdHlZdWo4OHoxOUFJaXhfMkkwc0VVak5OMHQ0MUNFR3RSSTRzMjJZd1JpOFpQNmp2NkJSLW5nRFE2aVl4VlphZ0Y1MnNFRHo3NVV4VFpRT25rZw?oc=5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="K23" s="1" t="n">
-        <v>46111.0595949074</v>
+        <v>46111.1737037037</v>
       </c>
     </row>
     <row r="24">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxObU1lb2ZVbUlvOXZEbHhYam1obW9uMHAtdzlTN1Vha2Y0MjJuYXZUWW5fSktURXl6V3JmUV9PbEZVUjRtUmFuYTZnUGJMN0syVnBBbHdtbk42RlRJZXpCbzBsUVJQczRkdzkwa25rLVBmdXJpcnVMdE0tRndTakp1S211S01wTTktOWstQkE3TjNwT2wzR0lnelNsdjZnTDVwVEVCXzVYVjNXakVW?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPeC1sVlI5R1hZRlplbk54cTRKLU1OMEtCM3dRWTJkZENjblhpTlRpQ2FQU19jQVZjbnNnbWNuS0pCRl94N1pPalRjWjhrWkhIa293ZFBCdkRNck5hTEdJXzI4dWRrUDJxbXFFWHdzc3lQaE9UZkRYRWdSOWdRRWNyNVBhY2kwUnJlcGtaVkozcTdUQnRWbGtSMTgzdjl2VzhDM2lQMTJLNFJ0TFhPY2VNaUJrMUZlLW11eVdrYW1wakpad0N1eWFtZXhYMA?oc=5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1800,32 +1800,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>Village Las Rozas La Roca (fallback)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Las Rozas Village" OR "La Roca Village" OR "Las Rozas" OR "La Roca") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Two men arrested over fatal stabbing of man, 26, in Westminster - London Evening Standard</t>
+          <t>Spain: Las Rozas Black Demons dominate on road, bounce back against Camioneros - American Football International</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Two men arrested over fatal stabbing of man, 26, in Westminster - London Evening Standard</t>
+          <t>Spain: Las Rozas Black Demons dominate on road, bounce back against Camioneros - American Football International</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 04:32:09 GMT</t>
+          <t>Mon, 30 Mar 2026 05:31:40 GMT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPNUZ0MHVUTEQ1X1JqaWN6UWxOUHF2QkhkNjMzeW4xVXkwSzI1YkttTEZoOXBOVlZRRnQwR0RaZGNoYTZTSkJ4UTlhSUkwQkwyLUxHeGtuR0NoY1JRUVpzTEVqQVM1NHI2NWJmcTYwRVlpTGZwYlNzbFM0VVVMb0RLODZVU3lTeDg2SDlvbm1yNXR4eFFm?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQODNGUDFfYlN0eXI5Ti14VllNQXc4aF9iZDhXYTRnU2RIVDlkNi1rVGlGaDVsQVBQWUtTaElvRDlhYnhFYWtvVlVpS1R2V2l0VVcxWGdTMS1HSkFUT0JrMTQtRVd3WGxPU3dKeG5xQnQzNnRCeGxnSWt3RTdzOC0wY3lIZ2FvWmlCLUJ5N2k0ZjMxMFhmeUtQVjZHa1dFWEVOTXh3a3pXYWZISmhGOEdXSnItWFNkQmU1NlVBS1RR0gG-AUFVX3lxTFA4M0ZQMV9iU3R5cjlOLXhWWU1BdzhoX2JkOFdhNGdTZEhUOWQ2LWtUaUZoNWxBUFBZS1NoSW9EOWFieEVha29WVWlLVHZXaXRVVzFYZ1MxLUdKQVRPQmsxNC1FV3dYbE9Td0p4bnFCdDM2dEJ4bGdJa3dFN3M4LTBjeUhnYW9aaUItQnk3aTRmMzEwWGZ5S1BWNkdrV0VYRU5NeHdreldhZkhKaEY4R1dKci1YU2RCZTU2VUFLVFE?oc=5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1849,38 +1849,38 @@
         </is>
       </c>
       <c r="K26" s="1" t="n">
-        <v>46111.18899305556</v>
+        <v>46111.23032407407</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Treni, nuovo sciopero di 24 ore in arrivo ad aprile - NovaraToday</t>
+          <t>Two men arrested over fatal stabbing of man, 26, in Westminster - London Evening Standard</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Trains, new 24-hour strike coming in April - NovaraToday</t>
+          <t>Two men arrested over fatal stabbing of man, 26, in Westminster - London Evening Standard</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 06:18:00 GMT</t>
+          <t>Mon, 30 Mar 2026 04:32:09 GMT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9VdjZOQjl3M1pSXzRlVWVNN3YxZldqc3dTUV9iU29mOEVYQ1lZNk81ZTBNR2Q2NWdQblE3RnlyekxjZ1NuQ2NNdmozNmU3SDZXSzJKbmZoZVFNS2k0emZHZDlmSlB4eEhvUXRySnR6aXZJVkt3TGNwc2JuYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPNUZ0MHVUTEQ1X1JqaWN6UWxOUHF2QkhkNjMzeW4xVXkwSzI1YkttTEZoOXBOVlZRRnQwR0RaZGNoYTZTSkJ4UTlhSUkwQkwyLUxHeGtuR0NoY1JRUVpzTEVqQVM1NHI2NWJmcTYwRVlpTGZwYlNzbFM0VVVMb0RLODZVU3lTeDg2SDlvbm1yNXR4eFFm?oc=5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1890,52 +1890,52 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K27" s="1" t="n">
-        <v>46111.2625</v>
+        <v>46111.18899305556</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Parcheggi spariti e incidenti, a Milano la nuova protesta contro le ciclabili - MSN</t>
+          <t>Euston shooting police hunt suspect who 'fled on bike' after man killed in car - The Mirror</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Disappeared parking spaces and accidents, the new protest against cycle paths in Milan - MSN</t>
+          <t>Euston shooting police hunt suspect who 'fled on bike' after man killed in car - The Mirror</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 03:26:02 GMT</t>
+          <t>Mon, 30 Mar 2026 07:24:00 GMT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNM01IT3ZVY0dLWTU5MUVOM2JtMzYwbE5PWl9uM2w5Z2pidHYzSlJtbGM2M2FOUkJ0eFZXWWxIU0xldTkxeEdUd3BZTVhwR2NXZ0dFM21QekplT0c2R1F1TV9NRjVDYnlDZEp0QlVGa1lGQXlVRW95WWpuLUVCNFFCaFZreHoxTWVIc201Z1MtRTMydzdnSUJnZDkzLXQ5QkJBcUVYZkczb2lGSm1aN2V5ZGMyMDRyWk9BUF9BTVFBbnhSZ1cyVDgzbl8xVC1SQXY3YlZQZXJ1c2ZUU3FFMUo0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQa0dfWWQ1aGFHd1ZwTjl3YTJPZngyeWl6b0s3RzdBcmhOUGhpNVhZZ0MwekNHZ3Q1RmdMUzluZGV5UVNxejRUaENSZHIzQ1ozWmY0U2o1Wk4xTXVvWjNfMTNhQ0VYdWF3RGFwbnRjeVY0M2JCN0FDaHBPRHU2SmpCQlhENzJDNGJfaVHSAY8BQVVfeXFMTkxoZ29SUVFjNU9DdlYzVmhqRjFKQkktYjl5U1lSTnQtU0thMG5aTXhteWI3ZFNEOGxRZng3cDRMSjN3VnZaM292Z2REMV9BYVlTWlB3dFFrczJSNGZqdXYxdmFmR081U083XzhjeFp1dWF2c2RqTXE0dFBPelFHbWdQTzhkcDFXN2ctZkRKRFU?oc=5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1945,52 +1945,52 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K28" s="1" t="n">
-        <v>46111.1430787037</v>
+        <v>46111.30833333333</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>Village La Vallee (fallback)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("La Vallee Village" OR "La Vallée Village" OR "Serris" OR "Chessy") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Il trasloco della Fiege a Stradella: "Inaccettabile, la lotta continua" - Il Giorno</t>
+          <t>Disney opens World of Frozen in Paris - Jamaica Gleaner</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Fiege's move to Stradella: "Unacceptable, the fight continues" - Il Giorno</t>
+          <t>Disney opens World of Frozen in Paris - Jamaica Gleaner</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 03:43:31 GMT</t>
+          <t>Mon, 30 Mar 2026 05:06:22 GMT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9Pdmh6b1pSblhPdDE2X1dZSDJXaFN4SHJjTTdGajVXbWNIbDQyal9RYjIyVGlWQVMtWXJkY3FqVkctZDJSN251QnNjUktZUEctN2pQd0Q1ZmdaeWlkbEh0d2FFUlpJN3F6NnNvOTg5TFZOUmU4dnlOeDNFbUF6QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNb2pMaTVOdWluRXhMaHJTU1dtcElaMEVSZWxYc1BiZWd3WHRFc09XQm9RcXBlU29YeG5iRnF6QzVUZXNsZzlaNWVqaHpLMkc3c1diN2FsUVZxUXFJa1ExMHlqNklUYjdEcG13eFpRTnZVUy1xVWtpUk0yT3B0dVZVYWhUSG9MVllrTU1iZmQ2MA?oc=5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2000,21 +2000,21 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K29" s="1" t="n">
-        <v>46111.15521990741</v>
+        <v>46111.21275462963</v>
       </c>
     </row>
     <row r="30">
@@ -2030,22 +2030,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Milano, De Corato: oltre mille iraniani davanti al consolato contro il regime degli ayatollah e a sostegno di Reza Pahlavi - Milano Post</t>
+          <t>Treni, nuovo sciopero di 24 ore in arrivo ad aprile - NovaraToday</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Milan, De Corato: over a thousand Iranians in front of the consulate against the ayatollah regime and in support of Reza Pahlavi - Milan Post</t>
+          <t>Trains, new 24-hour strike coming in April - NovaraToday</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 05:58:27 GMT</t>
+          <t>Mon, 30 Mar 2026 06:18:00 GMT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxPTUhxQzBxWXJnejJEY3lrcGJUaWhNVDZaeVpOb2lWUjVTOHowLXE4TU1BUGd3OXpBVDRmamhCUHRXU29IZ3pCMHBOT2RHYi1TU2cxbXIwcXhtQi1wTFVTankzdE9jcnZlaGctdWxORHZiRjN3U2F4N2tMSjdPZkhqalNZZVlMdm1jYmFmTmlWQUtnX2pPMmFFdExqVmw1RUFKeVM5Y1pSM2FnVG9VYzcwLXhoTmk1M0tWMjR2Z0ZWNUdLUDNMRVgtQnlZaGxIZjNMRmZZeUwzdXF4VXNsdGtlMlBKdnJvUkxGZjBnbmUzakdoUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9VdjZOQjl3M1pSXzRlVWVNN3YxZldqc3dTUV9iU29mOEVYQ1lZNk81ZTBNR2Q2NWdQblE3RnlyekxjZ1NuQ2NNdmozNmU3SDZXSzJKbmZoZVFNS2k0emZHZDlmSlB4eEhvUXRySnR6aXZJVkt3TGNwc2JuYw?oc=5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="K30" s="1" t="n">
-        <v>46111.24892361111</v>
+        <v>46111.2625</v>
       </c>
     </row>
     <row r="31">
@@ -2085,46 +2085,266 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>Il trasloco della Fiege a Stradella: "Inaccettabile, la lotta continua" - Il Giorno</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Fiege's move to Stradella: "Unacceptable, the fight continues" - Il Giorno</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mon, 30 Mar 2026 03:43:31 GMT</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9Pdmh6b1pSblhPdDE2X1dZSDJXaFN4SHJjTTdGajVXbWNIbDQyal9RYjIyVGlWQVMtWXJkY3FqVkctZDJSN251QnNjUktZUEctN2pQd0Q1ZmdaeWlkbEh0d2FFUlpJN3F6NnNvOTg5TFZOUmU4dnlOeDNFbUF6QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K31" s="1" t="n">
+        <v>46111.15521990741</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sciopero aerei 10 aprile 2026: venerdì nero per i voli. Orari, cancellazioni e la lista dei garantiti - BusinessMobility.travel</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Aircraft strike 10 April 2026: Black Friday for flights. Timetables, cancellations and the guaranteed list - BusinessMobility.travel</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Mon, 30 Mar 2026 07:42:45 GMT</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNRTdBR1BaSHpVT0xCcE1GclBDNWxINUpEM3l4bVk4aVdYUGV0ZGk3T0o1SGdGUUtEUzY4ekZlcEhVZHFmTTJ6Y081YWdnbUo1MUZPYjBWLXRvaGs1SDNRbGIyek9MUHJmVjlDeTFrNE16dmpTWmVuclhoV1VEb2NxaHM4MmY0LVhtS29BX21iT0o2WDNSY1dSR1RRWk96dGhWLV9MUlZNaElKQi01WThYa2FJYnVUcS1NLTV4N0J5VmxjNU5VOWFTS25DeFlzWjUzY3pwRk5HS04?oc=5</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K32" s="1" t="n">
+        <v>46111.32135416667</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Milano, De Corato: oltre mille iraniani davanti al consolato contro il regime degli ayatollah e a sostegno di Reza Pahlavi - milanopost.info</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Milan, De Corato: over a thousand Iranians in front of the consulate against the ayatollah regime and in support of Reza Pahlavi - milanopost.info</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Mon, 30 Mar 2026 05:58:27 GMT</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxPTUhxQzBxWXJnejJEY3lrcGJUaWhNVDZaeVpOb2lWUjVTOHowLXE4TU1BUGd3OXpBVDRmamhCUHRXU29IZ3pCMHBOT2RHYi1TU2cxbXIwcXhtQi1wTFVTankzdE9jcnZlaGctdWxORHZiRjN3U2F4N2tMSjdPZkhqalNZZVlMdm1jYmFmTmlWQUtnX2pPMmFFdExqVmw1RUFKeVM5Y1pSM2FnVG9VYzcwLXhoTmk1M0tWMjR2Z0ZWNUdLUDNMRVgtQnlZaGxIZjNMRmZZeUwzdXF4VXNsdGtlMlBKdnJvUkxGZjBnbmUzakdoUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K33" s="1" t="n">
+        <v>46111.24892361111</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>Invasione di bassotti in centro. Il ritorno della ’Sausage Walk’ - Il Giorno</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Invasion of dachshunds in the center. The return of the 'Sausage Walk' - The Day</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 02:48:23 GMT</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQLVpZUmkwRmlqNnlDVldpNU41SWxqWWtCMmRGZ1dacVY5RC1yMndCckJURkg4R2RyR3h2TjRzS1F2LUtvZHNGclA5TlBKNnlXT2VrWVBhSl81dDA0UDdqRjVTZkhHamx6TW1NdUR3UTVuWGNpT0c1LU01X0lWdDVWWGQ4OTB6Zw?oc=5</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>it</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>IT:it</t>
         </is>
       </c>
-      <c r="K31" s="1" t="n">
+      <c r="K34" s="1" t="n">
         <v>46111.11693287037</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Cronaca. Bologna, evasione dal carcere minorile del Pratello: il secondo fuggitivo fermato a Forlì - GiornaleSM</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>News. Bologna, escape from Pratello juvenile prison: the second fugitive arrested in Forlì - GiornaleSM</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Mon, 30 Mar 2026 08:03:16 GMT</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQVVdSRjhjbW43eG04ZkJXLTBCd3VIaklleWJlblU0bTBLclkzV1hQLWZDYXFWeDN0OWZVM3A3Z1ZqRkhFMmVKeVJVN216ZmpLTUgzVF9CeC03Y2Q0aENtcHdLSEN1clJqNHpkeHNpd01jbW1weW02NEZkekRReXdCU3hQZExFT0stWDlGV3czWjYyTG1HQmdzaGtXQ2FyVllCWWpQZ3hBdGNMMlBsWVM4bWNMYWpNOUtrUF9n?oc=5</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K35" s="1" t="n">
+        <v>46111.33560185185</v>
       </c>
     </row>
   </sheetData>
